--- a/public/downloads/BS2018_v100test.xlsx
+++ b/public/downloads/BS2018_v100test.xlsx
@@ -747,13 +747,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="3">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3">
         <v>10</v>
       </c>
       <c r="D3" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E3" s="3">
         <v>2</v>
@@ -762,16 +762,16 @@
         <v>6</v>
       </c>
       <c r="G3" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H3" s="4">
-        <v>1.191592276605855</v>
+        <v>1.225070769622334</v>
       </c>
       <c r="I3" s="4">
-        <v>0.7917334702004826</v>
+        <v>0.5168243159602807</v>
       </c>
       <c r="J3" s="4">
-        <v>1.272789417143043</v>
+        <v>1.306666810348042</v>
       </c>
       <c r="K3" s="4">
         <v>77.94353741496602</v>
@@ -1038,13 +1038,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="5">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" s="5">
         <v>5</v>
       </c>
       <c r="D3" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="5">
         <v>1</v>
@@ -1053,7 +1053,7 @@
         <v>3</v>
       </c>
       <c r="G3" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H3" s="5">
         <v>1</v>
@@ -1236,13 +1236,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>0.7038003405180159</v>
+        <v>0.7394055402692175</v>
       </c>
       <c r="O3" s="5">
         <v>15</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8909900970235244</v>
+        <v>0.8888956735087478</v>
       </c>
       <c r="Q3" s="4">
         <v>0.5717103795043711</v>
@@ -1295,22 +1295,22 @@
         <v>4</v>
       </c>
       <c r="N4" s="4">
-        <v>1.221693994395612</v>
+        <v>0.2582888030378854</v>
       </c>
       <c r="O4" s="5">
         <v>12</v>
       </c>
       <c r="P4" s="4">
-        <v>1.59340999472089</v>
+        <v>1.660991601598198</v>
       </c>
       <c r="Q4" s="4">
-        <v>1.211178475109145</v>
+        <v>0.1975654002440024</v>
       </c>
       <c r="R4" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S4" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1">
@@ -1354,16 +1354,16 @@
         <v>3</v>
       </c>
       <c r="N5" s="4">
-        <v>1.183243101581866</v>
+        <v>0.8384420580823644</v>
       </c>
       <c r="O5" s="5">
         <v>14</v>
       </c>
       <c r="P5" s="4">
-        <v>1.084050766914856</v>
+        <v>1.119090925268665</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.7338433223311162</v>
+        <v>0.6656298523030273</v>
       </c>
       <c r="R5" s="5">
         <v>12</v>
